--- a/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostDetailImport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostDetailImport.xlsx
@@ -29,38 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>发货单号</t>
-    </r>
-  </si>
-  <si>
-    <t>业务单号</t>
-  </si>
-  <si>
-    <t>店铺</t>
-  </si>
-  <si>
-    <t>仓库</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <r>
       <rPr>
@@ -87,26 +56,7 @@
     <t>产品名称</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>初始签收数量</t>
-    </r>
+    <t>单位(pcs)</t>
   </si>
   <si>
     <r>
@@ -122,138 +72,15 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>期初在途头程费用</t>
+      <t>单位成本</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>期初在途头程关税</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>期初暂估头程费用</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>期初暂估头程关税</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>分摊重量(KG)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>产品成本</t>
-    </r>
-  </si>
-  <si>
-    <t>币种（默认CNY）</t>
-  </si>
-  <si>
-    <t>{.sourceCode}</t>
-  </si>
-  <si>
-    <t>{.businessCode}</t>
-  </si>
-  <si>
-    <t>{.shopName}</t>
-  </si>
-  <si>
-    <t>{.warehouseName}</t>
+    <t>币种(默认CNY)</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -262,22 +89,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.initReceiveQty}</t>
-  </si>
-  <si>
-    <t>{.initTransitCost}</t>
-  </si>
-  <si>
-    <t>{.initTransitTariff}</t>
-  </si>
-  <si>
-    <t>{.initEstimatedCost}</t>
-  </si>
-  <si>
-    <t>{.initEstimatedTariff}</t>
-  </si>
-  <si>
-    <t>{.weightAllocation}</t>
+    <t>{.unit}</t>
   </si>
   <si>
     <t>{.productCost}</t>
@@ -290,16 +102,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
-    <numFmt numFmtId="178" formatCode="0.000000_ "/>
+    <numFmt numFmtId="176" formatCode="0.000000_ "/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,6 +267,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -909,29 +726,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1245,111 +1053,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
     <col min="3" max="3" width="14.75" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
+    <col min="4" max="4" width="21.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.875" customWidth="1"/>
-    <col min="6" max="6" width="20.25" customWidth="1"/>
-    <col min="7" max="7" width="17.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="20.375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="4" t="s">
+    <row r="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="E2" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
